--- a/Assets/Resource/Magic/Skill.xlsx
+++ b/Assets/Resource/Magic/Skill.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
   <si>
     <t>概率增加</t>
   </si>
@@ -41,10 +41,7 @@
     <t>骰王强运</t>
   </si>
   <si>
-    <t>每次投掷骰子之后，都会自动锁定其点数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">之后需要投掷时，需要选择：
+    <t xml:space="preserve">每次投掷骰子之后，都会自动锁定其点数，之后需要投掷时，需要选择：
 1.直接使用锁定点数为结果，然后被锁定的点数将加一。
 2.重新投掷，新的结果将覆盖原有的锁定结果。
 3.不使用点数也不重投，直接判定失败。</t>
@@ -116,19 +113,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>每&lt;s&gt;主动使用&lt;/s&gt;一张&lt;s&gt;水属性&lt;/s&gt;法术，摸一张牌。</t>
+    <t>每&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;水属性&lt;/u&gt;法术，摸一张牌。</t>
   </si>
   <si>
     <t>瀑流</t>
   </si>
   <si>
-    <t>每&lt;s&gt;主动使用&lt;/s&gt;一张&lt;s&gt;草属性&lt;/s&gt;法术，摸一张牌。</t>
+    <t>每&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;草属性&lt;/u&gt;法术，摸一张牌。</t>
   </si>
   <si>
     <t>寒流</t>
   </si>
   <si>
-    <t>主动使用一张水属性法术且命中时，有&lt;s&gt;1/3&lt;/s&gt;的概率可以选择弃掉目标的一张牌。</t>
+    <t>主动使用一张水属性法术且命中时，有&lt;u&gt;1/3&lt;/u&gt;的概率可以选择弃掉目标的一张牌。</t>
   </si>
   <si>
     <t>弃牌是在对方完成伤害结算之后。</t>
@@ -152,25 +149,25 @@
     <t>雾隐</t>
   </si>
   <si>
-    <t>每&lt;s&gt;主动使用&lt;/s&gt;一张&lt;s&gt;水属性&lt;/s&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
+    <t>每&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;水属性&lt;/u&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
   </si>
   <si>
     <t>沼泽</t>
   </si>
   <si>
-    <t>每&lt;s&gt;主动使用&lt;/s&gt;一张&lt;s&gt;草属性&lt;/s&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
+    <t>每&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;草属性&lt;/u&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
   </si>
   <si>
     <t>蒸汽锅炉</t>
   </si>
   <si>
-    <t>每主动使用一张&lt;s&gt;水属性&lt;/s&gt;法术，额外附带一点&lt;s&gt;火属性&lt;/s&gt;伤害。</t>
+    <t>每主动使用一张&lt;u&gt;水属性&lt;/u&gt;法术，额外附带一点&lt;u&gt;火属性&lt;/u&gt;伤害。</t>
   </si>
   <si>
     <t>烧伤</t>
   </si>
   <si>
-    <t>每主动使用一张&lt;s&gt;火属性&lt;/s&gt;法术，额外附带一点&lt;s&gt;火属性&lt;/s&gt;伤害。</t>
+    <t>每主动使用一张&lt;u&gt;火属性&lt;/u&gt;法术，额外附带一点&lt;u&gt;火属性&lt;/u&gt;伤害。</t>
   </si>
   <si>
     <t>大爆炸</t>
@@ -182,7 +179,7 @@
     <t>重燃</t>
   </si>
   <si>
-    <t>每&lt;s&gt;主动弃掉&lt;/s&gt;一张火属性法术牌，摸一张牌。</t>
+    <t>每&lt;u&gt;主动弃掉&lt;/u&gt;一张火属性法术牌，摸一张牌。</t>
   </si>
   <si>
     <t>火雨</t>
@@ -194,13 +191,13 @@
     <t>熔岩之甲</t>
   </si>
   <si>
-    <t>被动时，可减少一点法力，抵挡一点&lt;s&gt;草属性&lt;/s&gt;或&lt;s&gt;万能属性&lt;/s&gt;伤害。</t>
+    <t>被动时，可减少一点法力，抵挡一点&lt;u&gt;草属性&lt;/u&gt;或&lt;u&gt;万能属性&lt;/u&gt;伤害。</t>
   </si>
   <si>
     <t>流火</t>
   </si>
   <si>
-    <t>被动时，可减少一点法力，抵挡一点&lt;s&gt;火属性&lt;/s&gt;或&lt;s&gt;万能属性&lt;/s&gt;伤害。</t>
+    <t>被动时，可减少一点法力，抵挡一点&lt;u&gt;火属性&lt;/u&gt;或&lt;u&gt;万能属性&lt;/u&gt;伤害。</t>
   </si>
   <si>
     <t>蒸腾</t>
@@ -209,20 +206,20 @@
     <t>3</t>
   </si>
   <si>
-    <t>&lt;s&gt;主动使用&lt;/s&gt;一张水属性法术时，可以将其转化为基础&lt;s&gt;草属性&lt;/s&gt;法术。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置水属性法术，可以转化为你弃置了一张&lt;s&gt;草属性&lt;/s&gt;法术。
+    <t>&lt;u&gt;主动使用&lt;/u&gt;一张水属性法术时，可以将其转化为基础&lt;u&gt;草属性&lt;/u&gt;法术。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置水属性法术，可以转化为你弃置了一张&lt;u&gt;草属性&lt;/u&gt;法术。
 转化过一次的牌不能二次转化。</t>
   </si>
   <si>
     <t>藤蔓</t>
   </si>
   <si>
-    <t>&lt;s&gt;主动使用&lt;/s&gt;一张草属性法术时，可以将其转化为基础&lt;s&gt;火属性&lt;/s&gt;法术。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置草属性法术，可以转化为你弃置了一张&lt;s&gt;火属性&lt;/s&gt;法术。
+    <t>&lt;u&gt;主动使用&lt;/u&gt;一张草属性法术时，可以将其转化为基础&lt;u&gt;火属性&lt;/u&gt;法术。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置草属性法术，可以转化为你弃置了一张&lt;u&gt;火属性&lt;/u&gt;法术。
 转化过一次的牌不能二次转化。</t>
   </si>
   <si>
@@ -238,10 +235,10 @@
     <t>毒粉</t>
   </si>
   <si>
-    <t>每主动使用一张草属性法术，对方将有&lt;s&gt;2/3&lt;/s&gt;的概率叠加一层中毒。</t>
-  </si>
-  <si>
-    <t>&lt;s&gt;你的主动回合结束时&lt;/s&gt;，对方每拥有两层中毒，造成一点草属性伤害，然后减少1层中毒</t>
+    <t>每主动使用一张草属性法术，对方将有&lt;u&gt;2/3&lt;/u&gt;的概率叠加一层中毒。</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;你的主动回合结束时&lt;/u&gt;，对方每拥有两层中毒，造成一点草属性伤害，然后减少1层中毒</t>
   </si>
   <si>
     <t>最多可以叠加5层。</t>
@@ -256,7 +253,7 @@
     <t>木盾</t>
   </si>
   <si>
-    <t>&lt;s&gt;被动使用&lt;/s&gt;一张草属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
+    <t>&lt;u&gt;被动使用&lt;/u&gt;一张草属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
   </si>
   <si>
     <t>若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置草属性法术，可以转化为你弃置的一张万能属性法术。</t>
@@ -265,7 +262,7 @@
     <t>脱水</t>
   </si>
   <si>
-    <t>&lt;s&gt;被动使用&lt;/s&gt;一张火属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
+    <t>&lt;u&gt;被动使用&lt;/u&gt;一张火属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
   </si>
   <si>
     <t>波动</t>
@@ -274,13 +271,13 @@
     <t>4</t>
   </si>
   <si>
-    <t>主动使用&lt;s&gt;万能属性&lt;/s&gt;法术时，有&lt;s&gt;1/2&lt;/s&gt;的概率，额外附带两点相同属性伤害</t>
+    <t>主动使用&lt;u&gt;万能属性&lt;/u&gt;法术时，有&lt;u&gt;1/2&lt;/u&gt;的概率，额外附带两点相同属性伤害</t>
   </si>
   <si>
     <t>回声</t>
   </si>
   <si>
-    <t>&lt;s&gt;主动使用&lt;/s&gt;一张&lt;s&gt;万能属性&lt;/s&gt;法术时，可以额外消耗两点法力，使该法术的效果再触发一次（相当于使用了两次法术）。</t>
+    <t>&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;万能属性&lt;/u&gt;法术时，可以额外消耗两点法力，使该法术的效果再触发一次（相当于使用了两次法术）。</t>
   </si>
   <si>
     <t xml:space="preserve">被打断时，额外消耗的法力不会返回。
@@ -302,7 +299,7 @@
     <t>绝缘</t>
   </si>
   <si>
-    <t>受到&lt;s&gt;万能属性&lt;/s&gt;法术攻击时，有&lt;s&gt;2/3&lt;/s&gt;的概率免疫其造成的基础伤害（无法免疫因技能而附加的伤害）。</t>
+    <t>受到&lt;u&gt;万能属性&lt;/u&gt;法术攻击时，有&lt;u&gt;2/3&lt;/u&gt;的概率免疫其造成的基础伤害（无法免疫因技能而附加的伤害）。</t>
   </si>
   <si>
     <t>基础伤害指的是法术本身的伤害，对万能斩仍然有效。</t>
@@ -311,7 +308,7 @@
     <t>黑暗守护</t>
   </si>
   <si>
-    <t>获得守护印记效果：&lt;s&gt;你的主动回合结束时&lt;/s&gt;，印记重置为一层。一层守护印记可以在被动时视为一张万能属性法术使用（且不消耗法力值）。</t>
+    <t>获得守护印记效果：&lt;u&gt;你的主动回合结束时&lt;/u&gt;，印记重置为一层。一层守护印记可以在被动时视为一张万能属性法术使用（且不消耗法力值）。</t>
   </si>
   <si>
     <t>若使用条件修饰为主动回合开始时，则守护印记可以在主动时使用，视为一张万能属性法术。</t>
@@ -332,7 +329,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>&lt;s&gt;你的主动回合结束时&lt;/s&gt;，增加一点法力值。</t>
+    <t>&lt;u&gt;你的主动回合结束时&lt;/u&gt;，增加一点法力值。</t>
   </si>
   <si>
     <t>星辰</t>
@@ -344,11 +341,11 @@
     <t>启示</t>
   </si>
   <si>
-    <t>&lt;s&gt;你的主动回合开始时&lt;/s&gt;，有&lt;s&gt;1/6&lt;/s&gt;的概率本回合获得启示效果：使用卡牌/技能效果结算完成后，恢复消耗掉的全部法力值。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">若使用条件修饰为你的主动回合结束时，只有1/6的概率，在整个被动期间都不会消耗法力。
-若使用条件修饰为当你受伤时，若是在你的被动回合时受伤，则有1/6的概率，在整个被动期间都不消耗法力；若是在你的主动回合时受伤，有1/6的概率，在该回合内不会消耗任何法力。</t>
+    <t>&lt;u&gt;你的主动回合开始时&lt;/u&gt;，有&lt;u&gt;1/6&lt;/u&gt;的概率本回合获得启示效果：使用卡牌/技能效果结算完成后，恢复因其消耗掉的法力值。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">若使用条件修饰为你的主动回合结束时，则有1/6的概率在整个被动期间获得启示效果。
+若使用条件修饰为当你受伤时，则有1/6的概率在受伤的回合内获得启示效果。</t>
   </si>
   <si>
     <t>结晶</t>
@@ -360,7 +357,7 @@
     <t>灵魂燃烧</t>
   </si>
   <si>
-    <t>主动时，可以使自己减少一点生命值（可以触发受伤效果），每回合最多发动一次。&lt;s&gt;当你受伤时&lt;/s&gt;，恢复X点法力值，X为你的已损失生命值。</t>
+    <t>主动时，可以使自己减少一点生命值（可以触发受伤效果），每回合最多发动一次。&lt;u&gt;当你受伤时&lt;/u&gt;，恢复X点法力值，X为你的已损失生命值。</t>
   </si>
   <si>
     <t>图腾</t>
@@ -372,7 +369,7 @@
     <t>魔力汲取</t>
   </si>
   <si>
-    <t>对敌方造成伤害时/当你受伤害时，有&lt;s&gt;2/3&lt;/s&gt;的概率使对方减少一点法力值，同时你恢复一点法力值。</t>
+    <t>对敌方造成伤害时/当你受伤害时，有&lt;u&gt;2/3&lt;/u&gt;的概率使对方减少一点法力值，同时你恢复一点法力值。</t>
   </si>
   <si>
     <t xml:space="preserve">主动受伤不触发该效果。
@@ -391,31 +388,31 @@
     <t>自愈</t>
   </si>
   <si>
-    <t>&lt;s&gt;你的主动回合开始时&lt;/s&gt;，如果生命值小于等于3，有&lt;s&gt;1/3&lt;/s&gt;的概率恢复一点生命值。</t>
+    <t>&lt;u&gt;你的主动回合开始时&lt;/u&gt;，如果生命值小于等于3，有&lt;u&gt;1/3&lt;/u&gt;的概率恢复一点生命值。</t>
   </si>
   <si>
     <t>贪婪</t>
   </si>
   <si>
-    <t>&lt;s&gt;你的主动回合结束时&lt;/s&gt;，如果你的手牌数小于等于4，你摸一张牌。</t>
+    <t>&lt;u&gt;你的主动回合结束时&lt;/u&gt;，如果你的手牌数小于等于4，你摸一张牌。</t>
   </si>
   <si>
     <t>嗜血</t>
   </si>
   <si>
-    <t>攻击造成了X点伤害时，有&lt;s&gt;1/2&lt;/s&gt;的概率恢复一点生命值，重复进行X次判定。</t>
+    <t>攻击造成了X点伤害时，有&lt;u&gt;1/2&lt;/u&gt;的概率恢复一点生命值，重复进行X次判定。</t>
   </si>
   <si>
     <t>杀戮本能</t>
   </si>
   <si>
-    <t>当你的攻击触发他人的死亡感应时，你摸一张牌。你的死亡感应触发时，&lt;s&gt;1/2&lt;/s&gt;概率你摸一张牌。</t>
+    <t>当你的攻击触发他人的死亡感应时，你摸一张牌。你的死亡感应触发时，&lt;u&gt;1/2&lt;/u&gt;概率你摸一张牌。</t>
   </si>
   <si>
     <t>极速反应</t>
   </si>
   <si>
-    <t>受到攻击时，有&lt;s&gt;1/6&lt;/s&gt;的概率闪避</t>
+    <t>受到攻击时，有&lt;u&gt;1/6&lt;/u&gt;的概率闪避</t>
   </si>
   <si>
     <t>伤害是大于一时，伤害每增加一点，概率增加1/6，但闪避成功时本回合下一次必定失败。</t>
@@ -476,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,13 +523,10 @@
       <c r="D3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>1</v>
@@ -541,12 +535,12 @@
         <v>2</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>1</v>
@@ -555,12 +549,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>1</v>
@@ -569,12 +563,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>1</v>
@@ -583,12 +577,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>1</v>
@@ -597,12 +591,12 @@
         <v>2</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>1</v>
@@ -611,12 +605,12 @@
         <v>2</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>1</v>
@@ -625,12 +619,12 @@
         <v>2</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>1</v>
@@ -639,12 +633,12 @@
         <v>2</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>1</v>
@@ -653,12 +647,12 @@
         <v>2</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>1</v>
@@ -667,646 +661,644 @@
         <v>2</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="0" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="0" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="0" t="s">
+      <c r="E16" s="0" t="s">
         <v>37</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="0" t="s">
+      <c r="E18" s="0" t="s">
         <v>42</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="0" t="s">
         <v>44</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="0" t="s">
         <v>46</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="0" t="s">
         <v>48</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="0" t="s">
         <v>50</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="0" t="s">
         <v>52</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="0" t="s">
         <v>54</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="0" t="s">
         <v>56</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="0" t="s">
         <v>58</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="0" t="s">
         <v>60</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="C28" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="0" t="s">
+      <c r="E28" s="0" t="s">
         <v>64</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="0" t="s">
+      <c r="E29" s="0" t="s">
         <v>67</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="0" t="s">
+      <c r="E30" s="0" t="s">
         <v>70</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="0" t="s">
+      <c r="E31" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="F31" s="0" t="s">
         <v>74</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="0" t="s">
         <v>76</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="0" t="s">
+      <c r="E33" s="0" t="s">
         <v>79</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="0" t="s">
         <v>81</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="0" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="C35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="0" t="s">
         <v>84</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="0" t="s">
+      <c r="E36" s="0" t="s">
         <v>87</v>
-      </c>
-      <c r="E36" s="0" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="0" t="s">
         <v>89</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="0" t="s">
         <v>91</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="0" t="s">
+      <c r="E39" s="0" t="s">
         <v>94</v>
-      </c>
-      <c r="E39" s="0" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="0" t="s">
+      <c r="E40" s="0" t="s">
         <v>97</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" s="0" t="s">
+      <c r="E41" s="0" t="s">
         <v>100</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="C42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" s="0" t="s">
         <v>103</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="0" t="s">
         <v>105</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="B44" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" s="0" t="s">
+      <c r="E44" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="F44" s="0" t="s">
         <v>109</v>
+      </c>
+      <c r="G44" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="H44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="0" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>120</v>
-      </c>
       <c r="C49" s="0" t="s">
         <v>2</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="F54" s="0" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="B55" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D55" s="0" t="s">
         <v>135</v>
-      </c>
-      <c r="E55" s="0" t="s">
-        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/Skill.xlsx
+++ b/Assets/Resource/Magic/Skill.xlsx
@@ -41,10 +41,7 @@
     <t>骰王强运</t>
   </si>
   <si>
-    <t xml:space="preserve">每次投掷骰子之后，都会自动锁定其点数，之后需要投掷时，需要选择：
-1.直接使用锁定点数为结果，然后被锁定的点数将加一。
-2.重新投掷，新的结果将覆盖原有的锁定结果。
-3.不使用点数也不重投，直接判定失败。</t>
+    <t>每次投掷骰子之后，都会自动锁定其点数，之后需要投掷时，需要选择：1.直接使用锁定点数为结果，然后被锁定的点数将加一。2.重新投掷，新的结果将覆盖原有的锁定结果。3.不使用点数也不重投，直接判定失败。</t>
   </si>
   <si>
     <t>主动弃置修饰</t>
@@ -113,19 +110,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>每&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;水属性&lt;/u&gt;法术，摸一张牌。</t>
+    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;水属性&lt;/u&gt;&lt;/mark&gt;法术，摸一张牌。</t>
   </si>
   <si>
     <t>瀑流</t>
   </si>
   <si>
-    <t>每&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;草属性&lt;/u&gt;法术，摸一张牌。</t>
+    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术，摸一张牌。</t>
   </si>
   <si>
     <t>寒流</t>
   </si>
   <si>
-    <t>主动使用一张水属性法术且命中时，有&lt;u&gt;1/3&lt;/u&gt;的概率可以选择弃掉目标的一张牌。</t>
+    <t>主动使用一张水属性法术且命中时，有&lt;u&gt;&lt;mark=???&gt;1/3&lt;/u&gt;&lt;/mark&gt;的概率可以选择弃掉目标的一张牌。</t>
   </si>
   <si>
     <t>弃牌是在对方完成伤害结算之后。</t>
@@ -149,25 +146,25 @@
     <t>雾隐</t>
   </si>
   <si>
-    <t>每&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;水属性&lt;/u&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
+    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;水属性&lt;/u&gt;&lt;/mark&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
   </si>
   <si>
     <t>沼泽</t>
   </si>
   <si>
-    <t>每&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;草属性&lt;/u&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
+    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
   </si>
   <si>
     <t>蒸汽锅炉</t>
   </si>
   <si>
-    <t>每主动使用一张&lt;u&gt;水属性&lt;/u&gt;法术，额外附带一点&lt;u&gt;火属性&lt;/u&gt;伤害。</t>
+    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;水属性&lt;/u&gt;&lt;/mark&gt;法术，额外附带一点&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
   </si>
   <si>
     <t>烧伤</t>
   </si>
   <si>
-    <t>每主动使用一张&lt;u&gt;火属性&lt;/u&gt;法术，额外附带一点&lt;u&gt;火属性&lt;/u&gt;伤害。</t>
+    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术，额外附带一点&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
   </si>
   <si>
     <t>大爆炸</t>
@@ -179,7 +176,7 @@
     <t>重燃</t>
   </si>
   <si>
-    <t>每&lt;u&gt;主动弃掉&lt;/u&gt;一张火属性法术牌，摸一张牌。</t>
+    <t>每&lt;u&gt;&lt;mark=???&gt;主动弃掉&lt;/u&gt;&lt;/mark&gt;一张火属性法术牌，摸一张牌。</t>
   </si>
   <si>
     <t>火雨</t>
@@ -191,13 +188,13 @@
     <t>熔岩之甲</t>
   </si>
   <si>
-    <t>被动时，可减少一点法力，抵挡一点&lt;u&gt;草属性&lt;/u&gt;或&lt;u&gt;万能属性&lt;/u&gt;伤害。</t>
+    <t>被动时，可减少一点法力，抵挡一点&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;或&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
   </si>
   <si>
     <t>流火</t>
   </si>
   <si>
-    <t>被动时，可减少一点法力，抵挡一点&lt;u&gt;火属性&lt;/u&gt;或&lt;u&gt;万能属性&lt;/u&gt;伤害。</t>
+    <t>被动时，可减少一点法力，抵挡一点&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;或&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
   </si>
   <si>
     <t>蒸腾</t>
@@ -206,21 +203,19 @@
     <t>3</t>
   </si>
   <si>
-    <t>&lt;u&gt;主动使用&lt;/u&gt;一张水属性法术时，可以将其转化为基础&lt;u&gt;草属性&lt;/u&gt;法术。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置水属性法术，可以转化为你弃置了一张&lt;u&gt;草属性&lt;/u&gt;法术。
-转化过一次的牌不能二次转化。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张水属性法术时，可以将其转化为基础&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术。</t>
+  </si>
+  <si>
+    <t>若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置水属性法术，可以转化为你弃置了一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术。转化过一次的牌不能二次转化。</t>
   </si>
   <si>
     <t>藤蔓</t>
   </si>
   <si>
-    <t>&lt;u&gt;主动使用&lt;/u&gt;一张草属性法术时，可以将其转化为基础&lt;u&gt;火属性&lt;/u&gt;法术。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置草属性法术，可以转化为你弃置了一张&lt;u&gt;火属性&lt;/u&gt;法术。
-转化过一次的牌不能二次转化。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张草属性法术时，可以将其转化为基础&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术。</t>
+  </si>
+  <si>
+    <t>若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置草属性法术，可以转化为你弃置了一张&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术。转化过一次的牌不能二次转化。</t>
   </si>
   <si>
     <t>致幻蘑菇</t>
@@ -235,10 +230,10 @@
     <t>毒粉</t>
   </si>
   <si>
-    <t>每主动使用一张草属性法术，对方将有&lt;u&gt;2/3&lt;/u&gt;的概率叠加一层中毒。</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;你的主动回合结束时&lt;/u&gt;，对方每拥有两层中毒，造成一点草属性伤害，然后减少1层中毒</t>
+    <t>每主动使用一张草属性法术，对方将有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率叠加一层中毒。</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，对方每拥有两层中毒，造成一点草属性伤害，然后减少1层中毒</t>
   </si>
   <si>
     <t>最多可以叠加5层。</t>
@@ -253,7 +248,7 @@
     <t>木盾</t>
   </si>
   <si>
-    <t>&lt;u&gt;被动使用&lt;/u&gt;一张草属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;被动使用&lt;/u&gt;&lt;/mark&gt;一张草属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
   </si>
   <si>
     <t>若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置草属性法术，可以转化为你弃置的一张万能属性法术。</t>
@@ -262,7 +257,7 @@
     <t>脱水</t>
   </si>
   <si>
-    <t>&lt;u&gt;被动使用&lt;/u&gt;一张火属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;被动使用&lt;/u&gt;&lt;/mark&gt;一张火属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
   </si>
   <si>
     <t>波动</t>
@@ -271,17 +266,16 @@
     <t>4</t>
   </si>
   <si>
-    <t>主动使用&lt;u&gt;万能属性&lt;/u&gt;法术时，有&lt;u&gt;1/2&lt;/u&gt;的概率，额外附带两点相同属性伤害</t>
+    <t>主动使用&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;法术时，有&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;的概率，额外附带两点相同属性伤害</t>
   </si>
   <si>
     <t>回声</t>
   </si>
   <si>
-    <t>&lt;u&gt;主动使用&lt;/u&gt;一张&lt;u&gt;万能属性&lt;/u&gt;法术时，可以额外消耗两点法力，使该法术的效果再触发一次（相当于使用了两次法术）。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">被打断时，额外消耗的法力不会返回。
-使用条件修饰为主动弃置时，也可以额外消耗2点，视为弃了两张。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;法术时，可以额外消耗两点法力，使该法术的效果再触发一次（相当于使用了两次法术）。</t>
+  </si>
+  <si>
+    <t>被打断时，额外消耗的法力不会返回。使用条件修饰为主动弃置时，也可以额外消耗2点，视为弃了两张。</t>
   </si>
   <si>
     <t>击穿</t>
@@ -299,7 +293,7 @@
     <t>绝缘</t>
   </si>
   <si>
-    <t>受到&lt;u&gt;万能属性&lt;/u&gt;法术攻击时，有&lt;u&gt;2/3&lt;/u&gt;的概率免疫其造成的基础伤害（无法免疫因技能而附加的伤害）。</t>
+    <t>受到&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;法术攻击时，有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率免疫其造成的基础伤害（无法免疫因技能而附加的伤害）。</t>
   </si>
   <si>
     <t>基础伤害指的是法术本身的伤害，对万能斩仍然有效。</t>
@@ -308,7 +302,7 @@
     <t>黑暗守护</t>
   </si>
   <si>
-    <t>获得守护印记效果：&lt;u&gt;你的主动回合结束时&lt;/u&gt;，印记重置为一层。一层守护印记可以在被动时视为一张万能属性法术使用（且不消耗法力值）。</t>
+    <t>获得守护印记效果：&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，印记重置为一层。一层守护印记可以在被动时视为一张万能属性法术使用（且不消耗法力值）。</t>
   </si>
   <si>
     <t>若使用条件修饰为主动回合开始时，则守护印记可以在主动时使用，视为一张万能属性法术。</t>
@@ -329,7 +323,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>&lt;u&gt;你的主动回合结束时&lt;/u&gt;，增加一点法力值。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，增加一点法力值。</t>
   </si>
   <si>
     <t>星辰</t>
@@ -341,11 +335,10 @@
     <t>启示</t>
   </si>
   <si>
-    <t>&lt;u&gt;你的主动回合开始时&lt;/u&gt;，有&lt;u&gt;1/6&lt;/u&gt;的概率本回合获得启示效果：使用卡牌/技能效果结算完成后，恢复因其消耗掉的法力值。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">若使用条件修饰为你的主动回合结束时，则有1/6的概率在整个被动期间获得启示效果。
-若使用条件修饰为当你受伤时，则有1/6的概率在受伤的回合内获得启示效果。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合开始时&lt;/u&gt;&lt;/mark&gt;，有&lt;u&gt;&lt;mark=???&gt;1/6&lt;/u&gt;&lt;/mark&gt;的概率本回合获得启示效果：使用卡牌/技能效果结算完成后，恢复因其消耗掉的法力值。</t>
+  </si>
+  <si>
+    <t>若使用条件修饰为你的主动回合结束时，则有1/6的概率在整个被动期间获得启示效果。若使用条件修饰为当你受伤时，则有1/6的概率在受伤的回合内获得启示效果。</t>
   </si>
   <si>
     <t>结晶</t>
@@ -357,7 +350,7 @@
     <t>灵魂燃烧</t>
   </si>
   <si>
-    <t>主动时，可以使自己减少一点生命值（可以触发受伤效果），每回合最多发动一次。&lt;u&gt;当你受伤时&lt;/u&gt;，恢复X点法力值，X为你的已损失生命值。</t>
+    <t>主动时，可以使自己减少一点生命值（可以触发受伤效果），每回合最多发动一次。&lt;u&gt;&lt;mark=???&gt;当你受伤时&lt;/u&gt;&lt;/mark&gt;，恢复X点法力值，X为你的已损失生命值。</t>
   </si>
   <si>
     <t>图腾</t>
@@ -369,11 +362,10 @@
     <t>魔力汲取</t>
   </si>
   <si>
-    <t>对敌方造成伤害时/当你受伤害时，有&lt;u&gt;2/3&lt;/u&gt;的概率使对方减少一点法力值，同时你恢复一点法力值。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">主动受伤不触发该效果。
-对方法力为零时，概率成功后你仍然可以恢复法力。</t>
+    <t>对敌方造成伤害时/当你受伤害时，有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率使对方减少一点法力值，同时你恢复一点法力值。</t>
+  </si>
+  <si>
+    <t>主动受伤不触发该效果。对方法力为零时，概率成功后你仍然可以恢复法力。</t>
   </si>
   <si>
     <t>机械心脏</t>
@@ -388,31 +380,31 @@
     <t>自愈</t>
   </si>
   <si>
-    <t>&lt;u&gt;你的主动回合开始时&lt;/u&gt;，如果生命值小于等于3，有&lt;u&gt;1/3&lt;/u&gt;的概率恢复一点生命值。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合开始时&lt;/u&gt;&lt;/mark&gt;，如果生命值小于等于3，有&lt;u&gt;&lt;mark=???&gt;1/3&lt;/u&gt;&lt;/mark&gt;的概率恢复一点生命值。</t>
   </si>
   <si>
     <t>贪婪</t>
   </si>
   <si>
-    <t>&lt;u&gt;你的主动回合结束时&lt;/u&gt;，如果你的手牌数小于等于4，你摸一张牌。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，如果你的手牌数小于等于4，你摸一张牌。</t>
   </si>
   <si>
     <t>嗜血</t>
   </si>
   <si>
-    <t>攻击造成了X点伤害时，有&lt;u&gt;1/2&lt;/u&gt;的概率恢复一点生命值，重复进行X次判定。</t>
+    <t>攻击造成了X点伤害时，有&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;的概率恢复一点生命值，重复进行X次判定。</t>
   </si>
   <si>
     <t>杀戮本能</t>
   </si>
   <si>
-    <t>当你的攻击触发他人的死亡感应时，你摸一张牌。你的死亡感应触发时，&lt;u&gt;1/2&lt;/u&gt;概率你摸一张牌。</t>
+    <t>当你的攻击触发他人的死亡感应时，你摸一张牌。你的死亡感应触发时，&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;概率你摸一张牌。</t>
   </si>
   <si>
     <t>极速反应</t>
   </si>
   <si>
-    <t>受到攻击时，有&lt;u&gt;1/6&lt;/u&gt;的概率闪避</t>
+    <t>受到攻击时，有&lt;u&gt;&lt;mark=???&gt;1/6&lt;/u&gt;&lt;/mark&gt;的概率闪避</t>
   </si>
   <si>
     <t>伤害是大于一时，伤害每增加一点，概率增加1/6，但闪避成功时本回合下一次必定失败。</t>
@@ -473,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,22 +1128,10 @@
       <c r="E44" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="F44" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="G44" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="H44" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="0" t="s">
-        <v>110</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B45" s="0" t="s">
         <v>102</v>
@@ -1160,12 +1140,12 @@
         <v>31</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B46" s="0" t="s">
         <v>102</v>
@@ -1174,12 +1154,12 @@
         <v>31</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B47" s="0" t="s">
         <v>102</v>
@@ -1188,29 +1168,29 @@
         <v>31</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B49" s="0" t="s">
         <v>119</v>
@@ -1219,26 +1199,26 @@
         <v>2</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B50" s="0" t="s">
         <v>119</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B51" s="0" t="s">
         <v>119</v>
@@ -1247,12 +1227,12 @@
         <v>31</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B52" s="0" t="s">
         <v>119</v>
@@ -1261,12 +1241,12 @@
         <v>31</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B53" s="0" t="s">
         <v>119</v>
@@ -1275,29 +1255,43 @@
         <v>31</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="E53" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="F53" s="0" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B54" s="0" t="s">
         <v>119</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D54" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="E54" s="0" t="s">
+      <c r="E55" s="0" t="s">
         <v>135</v>
       </c>
     </row>

--- a/Assets/Resource/Magic/Skill.xlsx
+++ b/Assets/Resource/Magic/Skill.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>概率增加</t>
   </si>
@@ -41,25 +41,16 @@
     <t>骰王强运</t>
   </si>
   <si>
-    <t>每次投掷骰子之后，都会自动锁定其点数，之后需要投掷时，需要选择：1.直接使用锁定点数为结果，然后被锁定的点数将加一。2.重新投掷，新的结果将覆盖原有的锁定结果。3.不使用点数也不重投，直接判定失败。</t>
-  </si>
-  <si>
-    <t>主动弃置修饰</t>
-  </si>
-  <si>
-    <t>触发条件为主动使用/被动使用等的卡牌，触发条件可以变更为主动弃置。</t>
-  </si>
-  <si>
-    <t>主动使用修饰</t>
-  </si>
-  <si>
-    <t>触发条件为主动弃置/被动使用等的卡牌，触发条件可以变更为主动使用。</t>
+    <t xml:space="preserve">每次投掷骰子之后，都会自动锁定其点数，之后需要投掷时，需要选择：
+1.直接使用锁定点数为结果，然后被锁定的点数将加一。
+2.重新投掷，新的结果将覆盖原有的锁定结果。
+3.不使用点数也不重投，直接判定失败。</t>
   </si>
   <si>
     <t>被动使用修饰</t>
   </si>
   <si>
-    <t>触发条件为主动使用/主动弃置等的技能，触发条件可以变更为被动使用。</t>
+    <t>触发条件为主动使用的技能，触发条件可以变更为被动使用。</t>
   </si>
   <si>
     <t>回合开始修饰</t>
@@ -110,19 +101,25 @@
     <t>1</t>
   </si>
   <si>
-    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;水属性&lt;/u&gt;&lt;/mark&gt;法术，摸一张牌。</t>
+    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张水属性法术，摸一张牌。</t>
   </si>
   <si>
     <t>瀑流</t>
   </si>
   <si>
-    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术，摸一张牌。</t>
+    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张草属性法术，摸一张牌。</t>
+  </si>
+  <si>
+    <t>旋涡</t>
+  </si>
+  <si>
+    <t>每主动使用一张万能属性法术，摸一张牌。</t>
   </si>
   <si>
     <t>寒流</t>
   </si>
   <si>
-    <t>主动使用一张水属性法术且命中时，有&lt;u&gt;&lt;mark=???&gt;1/3&lt;/u&gt;&lt;/mark&gt;的概率可以选择弃掉目标的一张牌。</t>
+    <t>主动使用一张&lt;u&gt;&lt;mark=???&gt;水属性&lt;/u&gt;&lt;/mark&gt;法术且命中时，有&lt;u&gt;&lt;mark=???&gt;1/3&lt;/u&gt;&lt;/mark&gt;的概率可以选择弃掉目标的一张牌。</t>
   </si>
   <si>
     <t>弃牌是在对方完成伤害结算之后。</t>
@@ -131,7 +128,7 @@
     <t>海涌</t>
   </si>
   <si>
-    <t>当本回合内没有使用任何一张手牌时，可以摸两张牌然后回合结束。</t>
+    <t>当本回合内没有使用任何一张手牌时，可以摸一张牌然后回合结束，如果摸牌之后仍然手牌数小于5，则再摸一张。</t>
   </si>
   <si>
     <t>冰封铠甲</t>
@@ -140,181 +137,179 @@
     <t>被动使用元素法术抵挡伤害时，可以额外抵挡一点伤害（可抵挡的类型不变）。</t>
   </si>
   <si>
-    <t>只对法术有效，对技能没有增强。</t>
-  </si>
-  <si>
     <t>雾隐</t>
   </si>
   <si>
-    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;水属性&lt;/u&gt;&lt;/mark&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
-  </si>
-  <si>
-    <t>沼泽</t>
+    <t>被动使用&lt;u&gt;&lt;mark=???&gt;水属性&lt;/u&gt;&lt;/mark&gt;法术时，可以消耗一点法力，抵挡一次任意的全部伤害。</t>
+  </si>
+  <si>
+    <t>霜冻</t>
+  </si>
+  <si>
+    <t>被动时，可减少一点法力，抵挡一点火属性或万能属性伤害。</t>
+  </si>
+  <si>
+    <t>蒸汽锅炉</t>
+  </si>
+  <si>
+    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;水属性&lt;/u&gt;&lt;/mark&gt;法术，额外附带一点&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
+  </si>
+  <si>
+    <t>烧伤</t>
+  </si>
+  <si>
+    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术，额外附带一点&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
+  </si>
+  <si>
+    <t>余烬</t>
+  </si>
+  <si>
+    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;法术，额外附带一点&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
+  </si>
+  <si>
+    <t>大爆炸</t>
+  </si>
+  <si>
+    <t>主动使用&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术时，可以选择额外消耗X点法力，然后额外附带X点相同属性伤害。</t>
+  </si>
+  <si>
+    <t>浴火</t>
+  </si>
+  <si>
+    <t>任意时刻可以发动该技能，发动后生命值立即归零，然后有&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;的概率回复一点生命值且总共投掷6次，并且恢复一点法力。此技能发动后自动损坏进入弃牌堆。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对该技能的修饰不会同时损坏。
+不会触发受伤效果。</t>
+  </si>
+  <si>
+    <t>火雨</t>
+  </si>
+  <si>
+    <t>当&lt;u&gt;&lt;mark=???&gt;你受伤时&lt;/u&gt;&lt;/mark&gt;，根据攻击你的元素法术的属性，获得对该属性伤害的免疫，免疫效果可以叠加，但此效果在该被动回合结束时消失。</t>
+  </si>
+  <si>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>当&lt;u&gt;&lt;mark=???&gt;你受伤时&lt;/u&gt;&lt;/mark&gt;，摸一张牌。</t>
+  </si>
+  <si>
+    <t>熔岩之甲</t>
+  </si>
+  <si>
+    <t>被动时，可以选择弃掉任意张手牌，然后获得（弃牌数-1）的护盾值。如果只剩一张手牌，则弃掉之后必定能获得1点护盾值。</t>
+  </si>
+  <si>
+    <t>蒸腾</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>主动使用一张水属性/万能属性法术时，可以将其转化为基础草属性法术。</t>
+  </si>
+  <si>
+    <t>转化过一次的牌不能二次转化。</t>
+  </si>
+  <si>
+    <t>枯萎</t>
+  </si>
+  <si>
+    <t>主动使用一张草属性/万能属性法术时，可以将其转化为基础火属性法术。</t>
+  </si>
+  <si>
+    <t>致幻蘑菇</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张草属性/火属性法术时，可以将其转化为基础万能属性法术。</t>
+  </si>
+  <si>
+    <t>毒粉</t>
+  </si>
+  <si>
+    <t>主动使用草属性法术时，获得一层印记，最多一层。主动回合结束时，印记清空，若存在印记，则对对方造成一点草属性伤害（不能触发任何技能效果）。</t>
+  </si>
+  <si>
+    <t>复苏</t>
+  </si>
+  <si>
+    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术时，你可以选择不造成任何伤害（包括技能的附加伤害），然后有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;概率回复一点生命值。</t>
+  </si>
+  <si>
+    <t>木盾</t>
+  </si>
+  <si>
+    <t>被动使用火/草属性法术时，可以抵挡一点任意属性的伤害。</t>
+  </si>
+  <si>
+    <t>藤蔓</t>
   </si>
   <si>
     <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
   </si>
   <si>
-    <t>蒸汽锅炉</t>
-  </si>
-  <si>
-    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;水属性&lt;/u&gt;&lt;/mark&gt;法术，额外附带一点&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
-  </si>
-  <si>
-    <t>烧伤</t>
-  </si>
-  <si>
-    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术，额外附带一点&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
-  </si>
-  <si>
-    <t>大爆炸</t>
-  </si>
-  <si>
-    <t>主动使用火属性法术时，可以选择额外消耗X点法力，然后额外附带X点相同属性伤害。</t>
-  </si>
-  <si>
-    <t>重燃</t>
-  </si>
-  <si>
-    <t>每&lt;u&gt;&lt;mark=???&gt;主动弃掉&lt;/u&gt;&lt;/mark&gt;一张火属性法术牌，摸一张牌。</t>
-  </si>
-  <si>
-    <t>火雨</t>
-  </si>
-  <si>
-    <t>当你受伤时，根据攻击你的元素法术的属性，获得对该属性伤害的免疫，免疫效果可以叠加，但此效果在该被动回合结束时消失。</t>
-  </si>
-  <si>
-    <t>熔岩之甲</t>
-  </si>
-  <si>
-    <t>被动时，可减少一点法力，抵挡一点&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;或&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
-  </si>
-  <si>
-    <t>流火</t>
-  </si>
-  <si>
-    <t>被动时，可减少一点法力，抵挡一点&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;或&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;伤害。</t>
-  </si>
-  <si>
-    <t>蒸腾</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张水属性法术时，可以将其转化为基础&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术。</t>
-  </si>
-  <si>
-    <t>若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置水属性法术，可以转化为你弃置了一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术。转化过一次的牌不能二次转化。</t>
-  </si>
-  <si>
-    <t>藤蔓</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张草属性法术时，可以将其转化为基础&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术。</t>
-  </si>
-  <si>
-    <t>若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置草属性法术，可以转化为你弃置了一张&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术。转化过一次的牌不能二次转化。</t>
-  </si>
-  <si>
-    <t>致幻蘑菇</t>
-  </si>
-  <si>
-    <t>主动使用法力牌时，可以将其转化为基础草属性法术。</t>
-  </si>
-  <si>
-    <t>转化过一次的牌不能二次转化。</t>
-  </si>
-  <si>
-    <t>毒粉</t>
-  </si>
-  <si>
-    <t>每主动使用一张草属性法术，对方将有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率叠加一层中毒。</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，对方每拥有两层中毒，造成一点草属性伤害，然后减少1层中毒</t>
-  </si>
-  <si>
-    <t>最多可以叠加5层。</t>
-  </si>
-  <si>
-    <t>共生</t>
-  </si>
-  <si>
-    <t>水/火/草属性法术被动使用时，可以额外抵挡一点相同属性的伤害。</t>
-  </si>
-  <si>
-    <t>木盾</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;被动使用&lt;/u&gt;&lt;/mark&gt;一张草属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
-  </si>
-  <si>
-    <t>若使用条件被修饰为主动弃置，技能效果可被解释为：主动弃置草属性法术，可以转化为你弃置的一张万能属性法术。</t>
-  </si>
-  <si>
-    <t>脱水</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;被动使用&lt;/u&gt;&lt;/mark&gt;一张火属性法术时，可以将其转化为基础万能属性法术且不消耗法力。</t>
-  </si>
-  <si>
-    <t>波动</t>
+    <t>助燃</t>
+  </si>
+  <si>
+    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
+  </si>
+  <si>
+    <t>回声</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>主动使用&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;法术时，有&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;的概率，额外附带两点相同属性伤害</t>
-  </si>
-  <si>
-    <t>回声</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;法术时，可以额外消耗两点法力，使该法术的效果再触发一次（相当于使用了两次法术）。</t>
-  </si>
-  <si>
-    <t>被打断时，额外消耗的法力不会返回。使用条件修饰为主动弃置时，也可以额外消耗2点，视为弃了两张。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张万能属性法术时，可以额外消耗两点法力，使该法术的效果再触发一次（相当于使用了两张牌）。</t>
+  </si>
+  <si>
+    <t>被打断时，额外消耗的法力不会返回。</t>
   </si>
   <si>
     <t>击穿</t>
   </si>
   <si>
-    <t>你所造成的万能属性伤害，只能被万能法术阻挡。</t>
-  </si>
-  <si>
-    <t>共振</t>
-  </si>
-  <si>
-    <t>当你的伤害的全部或者部分被万能法术所阻挡时，你摸一张牌。</t>
-  </si>
-  <si>
-    <t>绝缘</t>
-  </si>
-  <si>
-    <t>受到&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;法术攻击时，有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率免疫其造成的基础伤害（无法免疫因技能而附加的伤害）。</t>
-  </si>
-  <si>
-    <t>基础伤害指的是法术本身的伤害，对万能斩仍然有效。</t>
+    <t>你所造成的万能属性伤害，只能被万能法术或者阻挡任意伤害的效果所阻挡。</t>
+  </si>
+  <si>
+    <t>水循环</t>
+  </si>
+  <si>
+    <t>每主动弃掉一张水属性法术牌，摸一张牌。</t>
+  </si>
+  <si>
+    <t>火循环</t>
+  </si>
+  <si>
+    <t>每主动弃掉一张火属性法术牌，摸一张牌。</t>
+  </si>
+  <si>
+    <t>草循环</t>
+  </si>
+  <si>
+    <t>每主动弃掉一张草属性法术牌，摸一张牌。</t>
+  </si>
+  <si>
+    <t>膨胀</t>
+  </si>
+  <si>
+    <t>使用万能属性法术不消耗法力。</t>
+  </si>
+  <si>
+    <t>庇护</t>
+  </si>
+  <si>
+    <t>有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率免疫&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;的伤害。</t>
   </si>
   <si>
     <t>黑暗守护</t>
   </si>
   <si>
-    <t>获得守护印记效果：&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，印记重置为一层。一层守护印记可以在被动时视为一张万能属性法术使用（且不消耗法力值）。</t>
-  </si>
-  <si>
-    <t>若使用条件修饰为主动回合开始时，则守护印记可以在主动时使用，视为一张万能属性法术。</t>
-  </si>
-  <si>
-    <t>螺旋</t>
-  </si>
-  <si>
-    <t>被动使用万能法术不消耗法力。</t>
-  </si>
-  <si>
-    <t>。</t>
+    <t>获得守护印记效果：&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，印记重置为一层。一层守护印记可以在被动时视为一张基础万能属性法术使用（且不消耗法力值）。</t>
+  </si>
+  <si>
+    <t>若使用条件修饰为主动回合开始时，则守护印记可以在主动时使用，视为一张基础万能属性法术。</t>
   </si>
   <si>
     <t>雷鸣</t>
@@ -323,7 +318,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，增加一点法力值。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，增加一点法力值；并且在被动时也可以使用法力牌。</t>
   </si>
   <si>
     <t>星辰</t>
@@ -335,22 +330,19 @@
     <t>启示</t>
   </si>
   <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合开始时&lt;/u&gt;&lt;/mark&gt;，有&lt;u&gt;&lt;mark=???&gt;1/6&lt;/u&gt;&lt;/mark&gt;的概率本回合获得启示效果：使用卡牌/技能效果结算完成后，恢复因其消耗掉的法力值。</t>
-  </si>
-  <si>
-    <t>若使用条件修饰为你的主动回合结束时，则有1/6的概率在整个被动期间获得启示效果。若使用条件修饰为当你受伤时，则有1/6的概率在受伤的回合内获得启示效果。</t>
+    <t>你的主动回合开始时，有&lt;u&gt;&lt;mark=???&gt;1/6&lt;/u&gt;&lt;/mark&gt;的概率本回合获得启示效果：使用任何法术都不消耗法力值（因为技能而消耗的法力值还是需要消耗）。</t>
   </si>
   <si>
     <t>结晶</t>
   </si>
   <si>
-    <t>增加四点法力值上限。</t>
+    <t>增加三点法力值上限（并不会同时增加法力值）。</t>
   </si>
   <si>
     <t>灵魂燃烧</t>
   </si>
   <si>
-    <t>主动时，可以使自己减少一点生命值（可以触发受伤效果），每回合最多发动一次。&lt;u&gt;&lt;mark=???&gt;当你受伤时&lt;/u&gt;&lt;/mark&gt;，恢复X点法力值，X为你的已损失生命值。</t>
+    <t>主动时，可以使自己减少一点生命值（可以触发受伤效果），每回合最多发动一次。当&lt;u&gt;&lt;mark=???&gt;你受伤时&lt;/u&gt;&lt;/mark&gt;，恢复X点法力值，X为你的已损失生命值。</t>
   </si>
   <si>
     <t>图腾</t>
@@ -359,55 +351,40 @@
     <t>每主动弃置一个元素法术，可以恢复一点法力值。</t>
   </si>
   <si>
-    <t>魔力汲取</t>
-  </si>
-  <si>
-    <t>对敌方造成伤害时/当你受伤害时，有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率使对方减少一点法力值，同时你恢复一点法力值。</t>
-  </si>
-  <si>
-    <t>主动受伤不触发该效果。对方法力为零时，概率成功后你仍然可以恢复法力。</t>
-  </si>
-  <si>
-    <t>机械心脏</t>
+    <t>元素之躯</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>生命时归零时，若法力值大于等于3，则减少3点法力，生命值恢复到1点，并且恢复死亡感应。</t>
+    <t>主动使用元素法术时，叠加一层印记，当印记的层数大于等于当前生命值之后，使用任何元素法术额外附带一点同属性伤害。印记将在主动回合结束时清空。</t>
   </si>
   <si>
     <t>自愈</t>
   </si>
   <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合开始时&lt;/u&gt;&lt;/mark&gt;，如果生命值小于等于3，有&lt;u&gt;&lt;mark=???&gt;1/3&lt;/u&gt;&lt;/mark&gt;的概率恢复一点生命值。</t>
-  </si>
-  <si>
-    <t>贪婪</t>
-  </si>
-  <si>
-    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，如果你的手牌数小于等于4，你摸一张牌。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合开始时&lt;/u&gt;&lt;/mark&gt;，有&lt;u&gt;&lt;mark=???&gt;1/3&lt;/u&gt;&lt;/mark&gt;的概率恢复一点生命值。</t>
+  </si>
+  <si>
+    <t>生命值上限为6。</t>
   </si>
   <si>
     <t>嗜血</t>
   </si>
   <si>
-    <t>攻击造成了X点伤害时，有&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;的概率恢复一点生命值，重复进行X次判定。</t>
+    <t>攻击使对方损失了X点生命值时，有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率恢复一点生命值，重复进行X次判定。如果超过了生命值上限，超过的部分转化为恢复相应点数的法力。</t>
   </si>
   <si>
     <t>杀戮本能</t>
   </si>
   <si>
-    <t>当你的攻击触发他人的死亡感应时，你摸一张牌。你的死亡感应触发时，&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;概率你摸一张牌。</t>
+    <t>当你的攻击触发他人的死亡感应时，你摸一张牌。你的死亡感应触发时，&lt;u&gt;&lt;mark=???&gt;1/3&lt;/u&gt;&lt;/mark&gt;概率你摸一张牌。</t>
   </si>
   <si>
     <t>极速反应</t>
   </si>
   <si>
-    <t>受到攻击时，有&lt;u&gt;&lt;mark=???&gt;1/6&lt;/u&gt;&lt;/mark&gt;的概率闪避</t>
-  </si>
-  <si>
-    <t>伤害是大于一时，伤害每增加一点，概率增加1/6，但闪避成功时本回合下一次必定失败。</t>
+    <t>受到攻击时，有&lt;u&gt;&lt;mark=???&gt;1/6&lt;/u&gt;&lt;/mark&gt;的概率闪避。伤害值大于一时，伤害每增加一点，概率增加1/6。但闪避成功时本回合下一次必定失败</t>
   </si>
   <si>
     <t>先计算技能修饰的概率增加，再计算伤害值的额外的概率增加。</t>
@@ -416,7 +393,7 @@
     <t>扭曲空间</t>
   </si>
   <si>
-    <t>仅在你的主动回合时，你可以将手牌放入扭曲空间当中或取出，最多能放入3张。</t>
+    <t>仅在你的主动回合时，你可以将手牌放入扭曲空间当中或取出，最多能放入2张。</t>
   </si>
   <si>
     <t>当该技能消失的时候，其中储存的牌也会消失。</t>
@@ -465,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,38 +610,38 @@
         <v>26</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>32</v>
@@ -675,29 +652,29 @@
         <v>33</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>34</v>
       </c>
+      <c r="E15" s="0" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="0" t="s">
         <v>37</v>
       </c>
     </row>
@@ -706,10 +683,10 @@
         <v>38</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>39</v>
@@ -720,99 +697,99 @@
         <v>40</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="0" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="0" t="s">
         <v>45</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="0" t="s">
         <v>47</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="0" t="s">
         <v>49</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="0" t="s">
         <v>51</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="0" t="s">
+      <c r="E24" s="0" t="s">
         <v>54</v>
       </c>
     </row>
@@ -824,7 +801,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>56</v>
@@ -838,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>58</v>
@@ -852,7 +829,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>60</v>
@@ -866,7 +843,7 @@
         <v>62</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>63</v>
@@ -883,416 +860,395 @@
         <v>62</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>66</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>62</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>62</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>62</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>62</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>62</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="0" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>105</v>
+        <v>96</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B45" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="0" t="s">
         <v>102</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>124</v>
+        <v>115</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="F54" s="0" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/Skill.xlsx
+++ b/Assets/Resource/Magic/Skill.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>概率增加</t>
   </si>
@@ -176,11 +176,11 @@
     <t>浴火</t>
   </si>
   <si>
-    <t>任意时刻可以发动该技能，发动后生命值立即归零，然后有&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;的概率回复一点生命值且总共投掷6次，并且恢复一点法力。此技能发动后自动损坏进入弃牌堆。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对该技能的修饰不会同时损坏。
-不会触发受伤效果。</t>
+    <t>任意时刻可以发动该技能，发动后生命值立即归零（不会触发受伤效果），然后恢复一点法力，有&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;的概率回复一点生命值且总共投掷6次。此技能发动后自动消失。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">若受伤导致生命值归零，该技能将立即发动。
+对该技能的修饰不会同时消失。</t>
   </si>
   <si>
     <t>火雨</t>
@@ -201,6 +201,9 @@
     <t>被动时，可以选择弃掉任意张手牌，然后获得（弃牌数-1）的护盾值。如果只剩一张手牌，则弃掉之后必定能获得1点护盾值。</t>
   </si>
   <si>
+    <t>每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
+  </si>
+  <si>
     <t>蒸腾</t>
   </si>
   <si>
@@ -228,7 +231,7 @@
     <t>毒粉</t>
   </si>
   <si>
-    <t>主动使用草属性法术时，获得一层印记，最多一层。主动回合结束时，印记清空，若存在印记，则对对方造成一点草属性伤害（不能触发任何技能效果）。</t>
+    <t>主动使用草属性法术时，获得一层印记，最多一层。主动回合结束时，若存在印记，则对对方造成一点草属性伤害（不能触发任何技能效果），然后印记清空。</t>
   </si>
   <si>
     <t>复苏</t>
@@ -246,13 +249,16 @@
     <t>藤蔓</t>
   </si>
   <si>
-    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
+    <t>每&lt;u&gt;&lt;mark=???&gt;主动使用&lt;/u&gt;&lt;/mark&gt;一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术，叠加一层护盾。</t>
   </si>
   <si>
     <t>助燃</t>
   </si>
   <si>
-    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术，叠加一层护盾，每一点护盾可以抵挡一点任意属性的伤害，护盾将在主动回合开始时消失。</t>
+    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术，叠加一层护盾。</t>
+  </si>
+  <si>
+    <t>每一点护盾可以抵挡一点任意属性的伤害。护盾将在主动回合开始时消失。</t>
   </si>
   <si>
     <t>回声</t>
@@ -333,6 +339,9 @@
     <t>你的主动回合开始时，有&lt;u&gt;&lt;mark=???&gt;1/6&lt;/u&gt;&lt;/mark&gt;的概率本回合获得启示效果：使用任何法术都不消耗法力值（因为技能而消耗的法力值还是需要消耗）。</t>
   </si>
   <si>
+    <t>如果使用条件被修饰为你的主动回合结束时，则有1/6的概率会在结束时获得启示效果，效果将会持续整个被动回合。</t>
+  </si>
+  <si>
     <t>结晶</t>
   </si>
   <si>
@@ -378,7 +387,7 @@
     <t>杀戮本能</t>
   </si>
   <si>
-    <t>当你的攻击触发他人的死亡感应时，你摸一张牌。你的死亡感应触发时，&lt;u&gt;&lt;mark=???&gt;1/3&lt;/u&gt;&lt;/mark&gt;概率你摸一张牌。</t>
+    <t>当你的攻击触发他人的死亡感应时，你摸一张牌。你的死亡感应触发时，有&lt;u&gt;&lt;mark=???&gt;1/3&lt;/u&gt;&lt;/mark&gt;概率你摸一张牌。</t>
   </si>
   <si>
     <t>极速反应</t>
@@ -834,421 +843,433 @@
       <c r="D27" s="0" t="s">
         <v>60</v>
       </c>
+      <c r="E27" s="0" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="0" t="s">
         <v>65</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="0" t="s">
-        <v>99</v>
-      </c>
       <c r="C45" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C49" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C50" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C52" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C53" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C54" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C55" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/Magic/Skill.xlsx
+++ b/Assets/Resource/Magic/Skill.xlsx
@@ -146,7 +146,7 @@
     <t>霜冻</t>
   </si>
   <si>
-    <t>被动时，可减少一点法力，抵挡一点火属性或万能属性伤害。</t>
+    <t>被动时，可减少一点法力，抵挡一点水/火/万能属性伤害。</t>
   </si>
   <si>
     <t>蒸汽锅炉</t>
@@ -173,7 +173,7 @@
     <t>主动使用&lt;u&gt;&lt;mark=???&gt;火属性&lt;/u&gt;&lt;/mark&gt;法术时，可以选择额外消耗X点法力，然后额外附带X点相同属性伤害。</t>
   </si>
   <si>
-    <t>浴火</t>
+    <t>重燃</t>
   </si>
   <si>
     <t>任意时刻可以发动该技能，发动后生命值立即归零（不会触发受伤效果），然后恢复一点法力，有&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;的概率回复一点生命值且总共投掷6次。此技能发动后自动消失。</t>
@@ -237,7 +237,7 @@
     <t>复苏</t>
   </si>
   <si>
-    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术时，你可以选择不造成任何伤害（包括技能的附加伤害），然后有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;概率回复一点生命值。</t>
+    <t>每主动使用一张&lt;u&gt;&lt;mark=???&gt;草属性&lt;/u&gt;&lt;/mark&gt;法术时，你可以选择不造成任何伤害并且不触发任何技能效果，然后回复一点生命值。</t>
   </si>
   <si>
     <t>木盾</t>
@@ -279,40 +279,40 @@
     <t>你所造成的万能属性伤害，只能被万能法术或者阻挡任意伤害的效果所阻挡。</t>
   </si>
   <si>
-    <t>水循环</t>
-  </si>
-  <si>
-    <t>每主动弃掉一张水属性法术牌，摸一张牌。</t>
-  </si>
-  <si>
-    <t>火循环</t>
-  </si>
-  <si>
-    <t>每主动弃掉一张火属性法术牌，摸一张牌。</t>
-  </si>
-  <si>
-    <t>草循环</t>
-  </si>
-  <si>
-    <t>每主动弃掉一张草属性法术牌，摸一张牌。</t>
-  </si>
-  <si>
-    <t>膨胀</t>
-  </si>
-  <si>
-    <t>使用万能属性法术不消耗法力。</t>
-  </si>
-  <si>
-    <t>庇护</t>
-  </si>
-  <si>
-    <t>有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率免疫&lt;u&gt;&lt;mark=???&gt;万能属性&lt;/u&gt;&lt;/mark&gt;的伤害。</t>
+    <t>风暴</t>
+  </si>
+  <si>
+    <t>主动使用万能法术或扣除一点法力时，自动获得一层风暴印记，每主动回合最多获得一次。到达3层时自动清空，并摸三张牌。</t>
+  </si>
+  <si>
+    <t>循环</t>
+  </si>
+  <si>
+    <t>每主动弃掉一张万能属性法术牌/法力牌，摸一张牌。</t>
+  </si>
+  <si>
+    <t>火焰吸收</t>
+  </si>
+  <si>
+    <t>被动使用万能法术抵挡火法术造成的伤害时，有&lt;u&gt;&lt;mark=???&gt;1/2&lt;/u&gt;&lt;/mark&gt;的概率恢复一点生命值。</t>
+  </si>
+  <si>
+    <t>水面反射</t>
+  </si>
+  <si>
+    <t>被动使用万能法术抵挡水法术造成的伤害时，获得一层反射印记，最多两层。主动回合时，每移除一层印记对对方造成一点水属性伤害（不触发技能效果）。</t>
+  </si>
+  <si>
+    <t>丛林庇护</t>
+  </si>
+  <si>
+    <t>有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率免疫草属性的伤害。</t>
   </si>
   <si>
     <t>黑暗守护</t>
   </si>
   <si>
-    <t>获得守护印记效果：&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，印记重置为一层。一层守护印记可以在被动时视为一张基础万能属性法术使用（且不消耗法力值）。</t>
+    <t>获得守护印记。&lt;u&gt;&lt;mark=???&gt;你的主动回合结束时&lt;/u&gt;&lt;/mark&gt;，印记重置为一层。一层守护印记可以在被动时视为一张基础万能属性法术使用（且不消耗法力值）。</t>
   </si>
   <si>
     <t>若使用条件修饰为主动回合开始时，则守护印记可以在主动时使用，视为一张基础万能属性法术。</t>
@@ -336,7 +336,7 @@
     <t>启示</t>
   </si>
   <si>
-    <t>你的主动回合开始时，有&lt;u&gt;&lt;mark=???&gt;1/6&lt;/u&gt;&lt;/mark&gt;的概率本回合获得启示效果：使用任何法术都不消耗法力值（因为技能而消耗的法力值还是需要消耗）。</t>
+    <t>&lt;u&gt;&lt;mark=???&gt;你的主动回合开始时&lt;/u&gt;&lt;/mark&gt;，有&lt;u&gt;&lt;mark=???&gt;1/6&lt;/u&gt;&lt;/mark&gt;的概率本回合获得启示效果：使用任何法术都不消耗法力值（因为技能而消耗的法力值还是需要消耗）。</t>
   </si>
   <si>
     <t>如果使用条件被修饰为你的主动回合结束时，则有1/6的概率会在结束时获得启示效果，效果将会持续整个被动回合。</t>
@@ -345,7 +345,7 @@
     <t>结晶</t>
   </si>
   <si>
-    <t>增加三点法力值上限（并不会同时增加法力值）。</t>
+    <t>增加三点法力值上限（并不会同时增加法力值）。除光芒以外的法力牌可以无视限制，必定恢复两点法力（包括凝露、火石、琥珀、流风）。</t>
   </si>
   <si>
     <t>灵魂燃烧</t>
@@ -381,7 +381,7 @@
     <t>嗜血</t>
   </si>
   <si>
-    <t>攻击使对方损失了X点生命值时，有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率恢复一点生命值，重复进行X次判定。如果超过了生命值上限，超过的部分转化为恢复相应点数的法力。</t>
+    <t>攻击使对方损失了X点生命值时，有&lt;u&gt;&lt;mark=???&gt;2/3&lt;/u&gt;&lt;/mark&gt;的概率恢复一点生命值，重复进行X次判定，其中判定失败时，恢复一点法力值。</t>
   </si>
   <si>
     <t>杀戮本能</t>
